--- a/data/trans_dic/IP18A03-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -663,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,18; 66,11</t>
+          <t>48,29; 66,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,93; 70,29</t>
+          <t>52,61; 70,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,07; 78,84</t>
+          <t>58,58; 78,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,62; 85,55</t>
+          <t>45,68; 94,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,58; 70,77</t>
+          <t>52,73; 70,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,68; 69,6</t>
+          <t>51,17; 70,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,88; 81,69</t>
+          <t>63,26; 82,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,21; 76,36</t>
+          <t>61,21; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,54; 66,45</t>
+          <t>53,93; 66,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,63; 67,65</t>
+          <t>54,26; 67,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64,24; 78,19</t>
+          <t>64,06; 77,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,6; 73,3</t>
+          <t>64,54; 95,09</t>
         </is>
       </c>
     </row>
@@ -803,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>77,8%</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,53; 70,51</t>
+          <t>62,7; 70,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,36; 69,33</t>
+          <t>61,6; 69,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,64; 70,17</t>
+          <t>62,77; 70,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,7; 49,58</t>
+          <t>67,12; 84,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,2; 70,42</t>
+          <t>62,84; 69,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,12; 71,23</t>
+          <t>64,06; 71,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,25; 68,72</t>
+          <t>61,79; 69,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,12; 42,77</t>
+          <t>71,03; 84,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63,81; 69,43</t>
+          <t>64,12; 69,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64,15; 69,49</t>
+          <t>64,06; 69,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63,17; 68,52</t>
+          <t>63,1; 68,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,06; 42,35</t>
+          <t>72,48; 83,09</t>
         </is>
       </c>
     </row>
@@ -943,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48,78; 61,72</t>
+          <t>49,44; 62,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,29; 73,22</t>
+          <t>60,5; 72,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,07; 65,76</t>
+          <t>52,43; 65,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,62; 44,01</t>
+          <t>65,74; 90,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,51; 65,5</t>
+          <t>52,41; 65,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,96; 68,94</t>
+          <t>56,43; 68,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,36; 67,16</t>
+          <t>54,18; 67,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,69; 40,37</t>
+          <t>61,79; 88,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52,87; 61,66</t>
+          <t>52,62; 62,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60,31; 69,1</t>
+          <t>59,93; 68,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55,98; 64,73</t>
+          <t>55,74; 64,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,81; 38,07</t>
+          <t>68,61; 86,42</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>78,45%</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,51; 65,82</t>
+          <t>59,6; 66,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,23; 68,19</t>
+          <t>61,9; 68,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,1; 68,02</t>
+          <t>62,04; 68,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,25; 45,82</t>
+          <t>69,78; 83,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,39; 67,48</t>
+          <t>61,09; 67,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,0; 68,93</t>
+          <t>62,91; 68,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,87; 67,93</t>
+          <t>61,77; 67,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,06; 39,72</t>
+          <t>73,5; 84,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61,4; 65,71</t>
+          <t>61,4; 65,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63,37; 67,65</t>
+          <t>63,56; 67,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62,88; 67,16</t>
+          <t>62,75; 67,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,45; 40,44</t>
+          <t>73,63; 82,62</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>41125</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53703</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38658</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5175</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46001</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>47093</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>46498</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>8161</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>87126</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>100796</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>85155</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>13336</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>34478; 47676</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>45506; 60688</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32892; 44230</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2989; 6197</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>39050; 52572</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>39667; 54608</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>40003; 51992</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5775; 9434</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>78443; 96307</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>88989; 110867</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>76476; 92832</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>10313; 15195</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>248760</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>277931</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>291038</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>50242</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>272851</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>319244</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>284751</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>72289</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>521611</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>597176</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>575789</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>122531</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>233458; 262811</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>261782; 294640</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>274364; 306689</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>44459; 55649</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>257195; 285786</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>301301; 335114</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>269613; 301676</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>64817; 77471</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>501187; 540829</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>573536; 621369</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>551132; 596688</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>114140; 130857</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>85702</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>104044</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>91461</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21916</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82750</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>102503</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>104743</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>24143</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>168452</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>206547</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>196205</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>46060</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>76280; 96463</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>94726; 113758</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>80775; 101468</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18099; 24990</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>73331; 91984</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>92369; 111657</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>93351; 115721</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>19098; 27404</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>154820; 182822</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>191940; 220329</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>181906; 210447</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>40094; 50505</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>375587</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>435678</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>421157</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>77333</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>401602</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>468840</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>435992</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>104593</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>777189</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>904518</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>857149</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>181926</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>356422; 394946</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>413497; 454263</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>401597; 440376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69996; 84020</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>380792; 418133</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>447643; 490076</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>415013; 455541</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>96721; 111564</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>749907; 803198</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>876940; 933441</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>827832; 884042</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>170762; 191593</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A03-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,29; 66,78</t>
+          <t>48,02; 66,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,61; 70,16</t>
+          <t>52,9; 70,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,58; 78,78</t>
+          <t>58,37; 78,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45,68; 94,68</t>
+          <t>45,04; 94,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,73; 70,99</t>
+          <t>52,78; 70,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,17; 70,45</t>
+          <t>51,58; 69,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,26; 82,22</t>
+          <t>63,35; 82,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,21; 100,0</t>
+          <t>54,67; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,93; 66,21</t>
+          <t>53,45; 66,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,26; 67,59</t>
+          <t>54,1; 67,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64,06; 77,76</t>
+          <t>64,53; 77,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,54; 95,09</t>
+          <t>66,3; 94,18</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,7; 70,59</t>
+          <t>62,97; 70,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,6; 69,34</t>
+          <t>61,67; 69,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,77; 70,17</t>
+          <t>62,57; 70,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67,12; 84,01</t>
+          <t>65,69; 84,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,84; 69,82</t>
+          <t>62,78; 70,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,06; 71,24</t>
+          <t>64,12; 71,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,79; 69,13</t>
+          <t>61,13; 69,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,03; 84,9</t>
+          <t>71,15; 85,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64,12; 69,19</t>
+          <t>63,93; 69,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64,06; 69,4</t>
+          <t>64,14; 69,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63,1; 68,32</t>
+          <t>63,45; 68,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,48; 83,09</t>
+          <t>72,13; 83,03</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,44; 62,52</t>
+          <t>49,06; 62,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,5; 72,66</t>
+          <t>60,06; 72,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,43; 65,86</t>
+          <t>52,76; 66,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65,74; 90,77</t>
+          <t>65,8; 90,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,41; 65,74</t>
+          <t>52,48; 65,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,43; 68,21</t>
+          <t>56,57; 69,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,18; 67,16</t>
+          <t>54,37; 66,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61,79; 88,66</t>
+          <t>60,94; 87,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52,62; 62,14</t>
+          <t>52,78; 61,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59,93; 68,79</t>
+          <t>59,85; 68,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55,74; 64,48</t>
+          <t>55,42; 64,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68,61; 86,42</t>
+          <t>67,61; 86,79</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,6; 66,04</t>
+          <t>59,76; 66,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,9; 68,0</t>
+          <t>62,21; 67,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,04; 68,04</t>
+          <t>62,12; 68,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69,78; 83,76</t>
+          <t>69,12; 83,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,09; 67,09</t>
+          <t>61,17; 67,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,91; 68,87</t>
+          <t>62,65; 68,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,77; 67,8</t>
+          <t>61,91; 67,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73,5; 84,78</t>
+          <t>73,8; 85,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61,4; 65,77</t>
+          <t>61,34; 65,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63,56; 67,66</t>
+          <t>63,29; 67,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62,75; 67,01</t>
+          <t>62,82; 67,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,63; 82,62</t>
+          <t>73,72; 83,08</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34478; 47676</t>
+          <t>34283; 47752</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45506; 60688</t>
+          <t>45759; 60578</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32892; 44230</t>
+          <t>32774; 43915</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2989; 6197</t>
+          <t>2948; 6200</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39050; 52572</t>
+          <t>39087; 52351</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39667; 54608</t>
+          <t>39979; 54038</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40003; 51992</t>
+          <t>40061; 51941</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5775; 9434</t>
+          <t>5157; 9434</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>78443; 96307</t>
+          <t>77741; 97049</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>88989; 110867</t>
+          <t>88727; 110516</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76476; 92832</t>
+          <t>77036; 92985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10313; 15195</t>
+          <t>10595; 15050</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>233458; 262811</t>
+          <t>234446; 261389</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>261782; 294640</t>
+          <t>262054; 293297</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>274364; 306689</t>
+          <t>273497; 306231</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44459; 55649</t>
+          <t>43512; 55816</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>257195; 285786</t>
+          <t>256968; 288236</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>301301; 335114</t>
+          <t>301610; 335978</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>269613; 301676</t>
+          <t>266733; 301444</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64817; 77471</t>
+          <t>64925; 78179</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>501187; 540829</t>
+          <t>499713; 541269</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>573536; 621369</t>
+          <t>574250; 621054</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>551132; 596688</t>
+          <t>554198; 596427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>114140; 130857</t>
+          <t>113600; 130754</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76280; 96463</t>
+          <t>75702; 96224</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94726; 113758</t>
+          <t>94039; 113770</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80775; 101468</t>
+          <t>81278; 101839</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18099; 24990</t>
+          <t>18114; 24950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>73331; 91984</t>
+          <t>73437; 91592</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92369; 111657</t>
+          <t>92600; 113348</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93351; 115721</t>
+          <t>93685; 115072</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19098; 27404</t>
+          <t>18835; 26991</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>154820; 182822</t>
+          <t>155299; 181726</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>191940; 220329</t>
+          <t>191683; 220331</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181906; 210447</t>
+          <t>180876; 210676</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40094; 50505</t>
+          <t>39512; 50723</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>356422; 394946</t>
+          <t>357395; 395617</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>413497; 454263</t>
+          <t>415593; 454096</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>401597; 440376</t>
+          <t>402102; 441011</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69996; 84020</t>
+          <t>69339; 83614</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>380792; 418133</t>
+          <t>381263; 419390</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>447643; 490076</t>
+          <t>445834; 488224</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>415013; 455541</t>
+          <t>415971; 454660</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>96721; 111564</t>
+          <t>97109; 111974</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>749907; 803198</t>
+          <t>749208; 804497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>876940; 933441</t>
+          <t>873192; 934448</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>827832; 884042</t>
+          <t>828723; 884751</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>170762; 191593</t>
+          <t>170971; 192659</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A03-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62,12%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60,75%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>73,53%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>86,93%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>57,6%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>62,08%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>68,85%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>79,07%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>62,12%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>73,53%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,02; 66,88</t>
+          <t>52,58; 70,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,9; 70,03</t>
+          <t>50,68; 69,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,37; 78,21</t>
+          <t>63,88; 81,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45,04; 94,73</t>
+          <t>58,9; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,78; 70,69</t>
+          <t>47,18; 66,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,58; 69,71</t>
+          <t>52,93; 70,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,35; 82,14</t>
+          <t>58,07; 78,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,67; 100,0</t>
+          <t>48,26; 94,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,45; 66,72</t>
+          <t>53,54; 66,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,1; 67,38</t>
+          <t>54,63; 67,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64,53; 77,89</t>
+          <t>64,24; 78,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,3; 94,18</t>
+          <t>64,05; 94,32</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>66,66%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>67,87%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>65,26%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>79,23%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>66,81%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>65,4%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>66,59%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>75,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>66,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>67,87%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>65,26%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,97; 70,2</t>
+          <t>63,2; 70,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,67; 69,02</t>
+          <t>64,12; 71,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,57; 70,06</t>
+          <t>61,25; 68,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,69; 84,27</t>
+          <t>71,45; 86,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,78; 70,42</t>
+          <t>62,53; 70,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,12; 71,43</t>
+          <t>61,36; 69,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,13; 69,08</t>
+          <t>62,64; 70,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,15; 85,68</t>
+          <t>63,82; 82,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63,93; 69,25</t>
+          <t>63,81; 69,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64,14; 69,37</t>
+          <t>64,15; 69,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63,45; 68,29</t>
+          <t>63,17; 68,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,13; 83,03</t>
+          <t>70,79; 82,26</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>59,14%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>62,62%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60,79%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76,8%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>55,54%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>66,45%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>59,37%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>79,6%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>59,14%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>62,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>60,79%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,06; 62,36</t>
+          <t>51,51; 65,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,06; 72,67</t>
+          <t>55,96; 68,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,76; 66,1</t>
+          <t>54,36; 67,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65,8; 90,63</t>
+          <t>60,75; 89,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,48; 65,46</t>
+          <t>48,78; 61,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,57; 69,24</t>
+          <t>60,29; 73,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,37; 66,78</t>
+          <t>53,07; 65,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>60,94; 87,32</t>
+          <t>62,01; 89,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52,78; 61,77</t>
+          <t>52,87; 61,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59,85; 68,8</t>
+          <t>60,31; 69,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55,42; 64,55</t>
+          <t>55,98; 64,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,61; 86,79</t>
+          <t>65,95; 85,49</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64,43%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>65,89%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>64,89%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>79,23%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>62,81%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>65,22%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>65,07%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77,09%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>64,43%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>65,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64,89%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,76; 66,15</t>
+          <t>61,39; 67,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,21; 67,98</t>
+          <t>63,0; 68,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,12; 68,13</t>
+          <t>61,87; 67,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69,12; 83,35</t>
+          <t>72,99; 84,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,17; 67,29</t>
+          <t>59,51; 65,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,65; 68,61</t>
+          <t>62,23; 68,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,91; 67,67</t>
+          <t>62,1; 68,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73,8; 85,09</t>
+          <t>67,41; 82,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61,34; 65,87</t>
+          <t>61,4; 65,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63,29; 67,73</t>
+          <t>63,37; 67,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62,82; 67,07</t>
+          <t>62,88; 67,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,72; 83,08</t>
+          <t>72,72; 82,04</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>46001</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47093</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46498</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7903</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>41125</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>53703</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>38658</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5175</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>46001</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>47093</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46498</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>12664</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34283; 47752</t>
+          <t>38938; 52411</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45759; 60578</t>
+          <t>39281; 53946</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32774; 43915</t>
+          <t>40396; 51654</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2948; 6200</t>
+          <t>5354; 9091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39087; 52351</t>
+          <t>33688; 47197</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39979; 54038</t>
+          <t>45782; 60801</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40061; 51941</t>
+          <t>32602; 44264</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5157; 9434</t>
+          <t>2873; 5646</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77741; 97049</t>
+          <t>77875; 96661</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>88727; 110516</t>
+          <t>89605; 110956</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77036; 92985</t>
+          <t>76687; 93348</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10595; 15050</t>
+          <t>9637; 14191</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>373</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>403</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>436</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>74</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>272851</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>319244</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>284751</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>66404</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>248760</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>277931</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>291038</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>272851</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>319244</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>284751</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>46878</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>122531</t>
+          <t>113282</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>234446; 261389</t>
+          <t>258686; 288220</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>262054; 293297</t>
+          <t>301591; 335071</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>273497; 306231</t>
+          <t>267278; 299871</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43512; 55816</t>
+          <t>59878; 72124</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>256968; 288236</t>
+          <t>232799; 262542</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>301610; 335978</t>
+          <t>260768; 294602</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>266733; 301444</t>
+          <t>273775; 306675</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64925; 78179</t>
+          <t>40354; 52325</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>499713; 541269</t>
+          <t>498747; 542655</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>574250; 621054</t>
+          <t>574330; 622169</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>554198; 596427</t>
+          <t>551776; 598491</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>113600; 130754</t>
+          <t>104085; 120952</t>
         </is>
       </c>
     </row>
@@ -1789,37 +1789,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>82750</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>102503</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>104743</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22136</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>85702</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>104044</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>91461</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21916</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>82750</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>102503</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>104743</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24143</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46060</t>
+          <t>42659</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>75702; 96224</t>
+          <t>72067; 91644</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94039; 113770</t>
+          <t>91612; 112850</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81278; 101839</t>
+          <t>93660; 115712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18114; 24950</t>
+          <t>17510; 25665</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>73437; 91592</t>
+          <t>75269; 95236</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92600; 113348</t>
+          <t>94388; 114632</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93685; 115072</t>
+          <t>81760; 101311</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18835; 26991</t>
+          <t>16328; 23615</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>155299; 181726</t>
+          <t>155552; 181404</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>191683; 220331</t>
+          <t>193149; 221297</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>180876; 210676</t>
+          <t>182690; 211262</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39512; 50723</t>
+          <t>36374; 47153</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>557</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>629</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>117</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>401602</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>468840</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>435992</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>96443</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>375587</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>435678</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>421157</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>77333</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>401602</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>468840</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>435992</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>104593</t>
+          <t>72162</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>181926</t>
+          <t>168605</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>357395; 395617</t>
+          <t>382608; 420603</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>415593; 454096</t>
+          <t>448290; 490476</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>402102; 441011</t>
+          <t>415725; 456400</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69339; 83614</t>
+          <t>88848; 103108</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>381263; 419390</t>
+          <t>355869; 393637</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>445834; 488224</t>
+          <t>415703; 455491</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>415971; 454660</t>
+          <t>401981; 440299</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>97109; 111974</t>
+          <t>64389; 78663</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>749208; 804497</t>
+          <t>749860; 802559</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>873192; 934448</t>
+          <t>874302; 933363</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>828723; 884751</t>
+          <t>829481; 885929</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>170971; 192659</t>
+          <t>157965; 178217</t>
         </is>
       </c>
     </row>
